--- a/ig/ch-elm/CodeSystem-ch-elm-observation-profile-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-observation-profile-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/CodeSystem-ch-elm-observation-profile-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-observation-profile-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/CodeSystem-ch-elm-observation-profile-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-observation-profile-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/StructureDefinition/ch-elm-observation-hiv-rec</t>
+  </si>
+  <si>
+    <t>http://fhir.ch/ig/ch-elm/StructureDefinition/ch-elm-observation-component-cpe-txt</t>
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/StructureDefinition/ch-elm-observation-pq-virl</t>
@@ -466,7 +469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -553,6 +556,16 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/ch-elm/CodeSystem-ch-elm-observation-profile-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-observation-profile-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
